--- a/source-data/contacte_branduri.xlsx
+++ b/source-data/contacte_branduri.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -674,7 +674,7 @@
     <row r="5" ht="26.4" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Revas</t>
+          <t>ALEKSANDER REVAS</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -998,7 +998,7 @@
     <row r="13" ht="26.4" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Self</t>
+          <t>SELF.READYTOWEAR</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -1078,7 +1078,7 @@
     <row r="15" ht="26.4" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Tearless</t>
+          <t>TEARLESS STREET</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -1320,7 +1320,7 @@
     <row r="21" ht="26.4" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>IAMIZA</t>
+          <t>I AM IZA</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -1400,7 +1400,7 @@
     <row r="23" ht="26.4" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Fena Clothing</t>
+          <t>FENA</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -1660,6 +1660,48 @@
       <c r="H29" s="4" t="inlineStr">
         <is>
           <t>Da - adiacent spatiului, permanent, 1.000 EUR/luna</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SITARA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>THE HOTULIGS S.R.L.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>office@sitaraclothing.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>+40 729 303 050</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Str. Constantin Brătescu, Nr. 18, Cam. 1, Constanța, jud. Constanța</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Str. Constantin Brătescu, Nr. 18, Constanța, jud. Constanța</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>necunoscut</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>necunoscut</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="27.77734375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1807,7 +1849,7 @@
     <row r="5" ht="25.05" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Revas</t>
+          <t>ALEKSANDER REVAS</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
@@ -1931,7 +1973,7 @@
     <row r="13" ht="25.05" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Self</t>
+          <t>SELF.READYTOWEAR</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
@@ -1961,7 +2003,7 @@
     <row r="15" ht="25.05" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Tearless</t>
+          <t>TEARLESS STREET</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
@@ -2053,7 +2095,7 @@
     <row r="21" ht="25.05" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>IAMIZA</t>
+          <t>I AM IZA</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
@@ -2083,7 +2125,7 @@
     <row r="23" ht="25.05" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Fena Clothing</t>
+          <t>FENA</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
@@ -2184,6 +2226,23 @@
       <c r="C29" s="4" t="inlineStr">
         <is>
           <t>Da - adiacent spatiului, permanent, 1.000 EUR/luna</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SITARA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>necunoscut</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>necunoscut</t>
         </is>
       </c>
     </row>

--- a/source-data/contacte_branduri.xlsx
+++ b/source-data/contacte_branduri.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1700,6 +1700,40 @@
         </is>
       </c>
       <c r="H30" t="inlineStr">
+        <is>
+          <t>necunoscut</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ANGEL TOUCH</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ANGEL TOUCH SRL</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>B-dul Timișoara, Nr. 53, Sector 6, București</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>B-dul Timișoara, Nr. 53, Sector 6, București</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>necunoscut</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
         <is>
           <t>necunoscut</t>
         </is>

--- a/source-data/contacte_branduri.xlsx
+++ b/source-data/contacte_branduri.xlsx
@@ -1058,12 +1058,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Drm. Gura Caliței, Nr. 4-32, Bl. 5, Sc. A, Ap. B23, Sector 3, București</t>
+          <t>București, Sectorul 3, Calea Moșilor, Nr. 88</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Drm. Gura Caliței, Nr. 4-32, Sector 3, București</t>
+          <t>București, Sectorul 3, Calea Moșilor, Nr. 88</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
@@ -1708,7 +1708,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ANGEL TOUCH</t>
+          <t>Green Lingerie Boutique</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1716,26 +1716,32 @@
           <t>ANGEL TOUCH SRL</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Lauramgherca@gmail.com; Greenlingerieboutique@gmail.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>+40 762 044 345</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t>B-dul Timișoara, Nr. 53, Bl. C2, Sc. 2, Et. 4, Ap. 40, Sector 6, București</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t>B-dul Timișoara, Nr. 53, Sector 6, București</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>B-dul Timișoara, Nr. 53, Sector 6, București</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>necunoscut</t>
-        </is>
+      <c r="G31" t="n">
+        <v>1</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>necunoscut</t>
+          <t>Nu</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="27.77734375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2280,6 +2286,21 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Green Lingerie Boutique</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" scale="95" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
